--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1577,6 +1577,960 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126017067</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78968</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>493304</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6867605</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126017069</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>493301</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6867607</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126017068</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80072</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>493301</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6867607</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126017433</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>493281</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6867643</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126017073</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>493393</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6867580</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126017066</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91228</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>493302</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6867571</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126017072</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80071</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>493413</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6867607</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126017070</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80072</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>493412</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6867608</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126017432</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80072</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öjingsvallen, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>493279</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6867644</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ängersjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-02</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -1897,7 +1897,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126017433</v>
+        <v>126017073</v>
       </c>
       <c r="B13" t="n">
         <v>80071</v>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493281</v>
+        <v>493393</v>
       </c>
       <c r="R13" t="n">
-        <v>6867643</v>
+        <v>6867580</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126017073</v>
+        <v>126017433</v>
       </c>
       <c r="B14" t="n">
         <v>80071</v>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493393</v>
+        <v>493281</v>
       </c>
       <c r="R14" t="n">
-        <v>6867580</v>
+        <v>6867643</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>126017067</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126017069</v>
+        <v>126017068</v>
       </c>
       <c r="B11" t="n">
-        <v>80071</v>
+        <v>80076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126017068</v>
+        <v>126017069</v>
       </c>
       <c r="B12" t="n">
-        <v>80072</v>
+        <v>80075</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1900,7 +1900,7 @@
         <v>126017073</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126017433</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>126017066</v>
       </c>
       <c r="B15" t="n">
-        <v>91228</v>
+        <v>91232</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>126017072</v>
       </c>
       <c r="B16" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>126017070</v>
       </c>
       <c r="B17" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>126017432</v>
       </c>
       <c r="B18" t="n">
-        <v>80072</v>
+        <v>80076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -1897,7 +1897,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126017073</v>
+        <v>126017433</v>
       </c>
       <c r="B13" t="n">
         <v>80075</v>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493393</v>
+        <v>493281</v>
       </c>
       <c r="R13" t="n">
-        <v>6867580</v>
+        <v>6867643</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,7 +2003,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126017433</v>
+        <v>126017073</v>
       </c>
       <c r="B14" t="n">
         <v>80075</v>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493281</v>
+        <v>493393</v>
       </c>
       <c r="R14" t="n">
-        <v>6867643</v>
+        <v>6867580</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>126017067</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>126017068</v>
       </c>
       <c r="B11" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>126017069</v>
       </c>
       <c r="B12" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126017433</v>
+        <v>126017073</v>
       </c>
       <c r="B13" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,10 +1936,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>493281</v>
+        <v>493393</v>
       </c>
       <c r="R13" t="n">
-        <v>6867643</v>
+        <v>6867580</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126017073</v>
+        <v>126017433</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>493393</v>
+        <v>493281</v>
       </c>
       <c r="R14" t="n">
-        <v>6867580</v>
+        <v>6867643</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2112,7 +2112,7 @@
         <v>126017066</v>
       </c>
       <c r="B15" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>126017072</v>
       </c>
       <c r="B16" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>126017070</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>126017432</v>
       </c>
       <c r="B18" t="n">
-        <v>80076</v>
+        <v>80077</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -2112,7 +2112,7 @@
         <v>126017066</v>
       </c>
       <c r="B15" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -2112,7 +2112,7 @@
         <v>126017066</v>
       </c>
       <c r="B15" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>126017067</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126017068</v>
+        <v>126017069</v>
       </c>
       <c r="B11" t="n">
-        <v>80077</v>
+        <v>80080</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126017069</v>
+        <v>126017068</v>
       </c>
       <c r="B12" t="n">
-        <v>80076</v>
+        <v>80081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1900,7 +1900,7 @@
         <v>126017073</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126017433</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>126017066</v>
       </c>
       <c r="B15" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>126017072</v>
       </c>
       <c r="B16" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>126017070</v>
       </c>
       <c r="B17" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>126017432</v>
       </c>
       <c r="B18" t="n">
-        <v>80077</v>
+        <v>80081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126017069</v>
+        <v>126017068</v>
       </c>
       <c r="B11" t="n">
-        <v>80080</v>
+        <v>80081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126017068</v>
+        <v>126017069</v>
       </c>
       <c r="B12" t="n">
-        <v>80081</v>
+        <v>80080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -1582,7 +1582,7 @@
         <v>126017067</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126017068</v>
+        <v>126017069</v>
       </c>
       <c r="B11" t="n">
-        <v>80081</v>
+        <v>80083</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126017069</v>
+        <v>126017068</v>
       </c>
       <c r="B12" t="n">
-        <v>80080</v>
+        <v>80084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1900,7 +1900,7 @@
         <v>126017073</v>
       </c>
       <c r="B13" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,7 +2006,7 @@
         <v>126017433</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>126017066</v>
       </c>
       <c r="B15" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>126017072</v>
       </c>
       <c r="B16" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
         <v>126017070</v>
       </c>
       <c r="B17" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>126017432</v>
       </c>
       <c r="B18" t="n">
-        <v>80081</v>
+        <v>80084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 63750-2019 artfynd.xlsx
+++ b/artfynd/A 63750-2019 artfynd.xlsx
@@ -1685,10 +1685,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126017069</v>
+        <v>126017068</v>
       </c>
       <c r="B11" t="n">
-        <v>80083</v>
+        <v>80084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1696,21 +1696,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1791,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126017068</v>
+        <v>126017069</v>
       </c>
       <c r="B12" t="n">
-        <v>80084</v>
+        <v>80083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,21 +1802,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
